--- a/output/pdf_financials_xlsx/CHY.H.xlsx
+++ b/output/pdf_financials_xlsx/CHY.H.xlsx
@@ -2056,43 +2056,43 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.027419</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.019745</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.09637999999999999</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.019243</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.007791</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.000531</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.01158</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.00548</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.246158</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.173315</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.06816899999999999</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.020231</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.196525</v>
       </c>
     </row>
     <row r="35">
@@ -2148,43 +2148,43 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.027419</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.019745</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.09637999999999999</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.019243</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.007791</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.000531</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.01158</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.00548</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.246158</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.173315</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.06816899999999999</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.020231</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.196525</v>
       </c>
     </row>
     <row r="37">
@@ -2700,16 +2700,16 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.028859</v>
+        <v>0.00144</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.022185</v>
+        <v>0.00244</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.096771</v>
+        <v>0.000391</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.019634</v>
+        <v>0.000391</v>
       </c>
       <c r="F48" s="3" t="n">
         <v>0</v>
@@ -6981,7 +6981,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -8059,7 +8059,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -19769,7 +19769,11 @@
           <t>General and administrative – Note 7</t>
         </is>
       </c>
-      <c r="D164" t="inlineStr"/>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E164" t="inlineStr">
         <is>
           <t>-</t>
@@ -20626,7 +20630,11 @@
           <t>General and administrative – Note 8</t>
         </is>
       </c>
-      <c r="D175" t="inlineStr"/>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E175" t="inlineStr">
         <is>
           <t>-</t>
@@ -21906,7 +21914,11 @@
           <t>General and administrative – Note 9</t>
         </is>
       </c>
-      <c r="D191" t="inlineStr"/>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E191" s="5" t="n">
         <v>0.206617</v>
       </c>

--- a/output/pdf_financials_xlsx/CHY.H.xlsx
+++ b/output/pdf_financials_xlsx/CHY.H.xlsx
@@ -1776,7 +1776,7 @@
         <v>0.0049</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>0.003185</v>
+        <v>0.003145</v>
       </c>
       <c r="F28" s="3" t="n">
         <v>0</v>
@@ -1822,7 +1822,7 @@
         <v>-0.104233</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.114618</v>
+        <v>-0.114658</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>-0.060746</v>
@@ -4648,43 +4648,43 @@
         </is>
       </c>
       <c r="B88" s="3" t="n">
-        <v>0</v>
+        <v>0.988117</v>
       </c>
       <c r="C88" s="3" t="n">
-        <v>0</v>
+        <v>0.993783</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>0</v>
+        <v>1.681949</v>
       </c>
       <c r="E88" s="3" t="n">
-        <v>0</v>
+        <v>1.681949</v>
       </c>
       <c r="F88" s="3" t="n">
-        <v>0</v>
+        <v>1.681949</v>
       </c>
       <c r="G88" s="3" t="n">
-        <v>0</v>
+        <v>1.681949</v>
       </c>
       <c r="H88" s="3" t="n">
-        <v>0</v>
+        <v>1.681949</v>
       </c>
       <c r="I88" s="3" t="n">
-        <v>0</v>
+        <v>1.681949</v>
       </c>
       <c r="J88" s="3" t="n">
-        <v>0</v>
+        <v>2.375173</v>
       </c>
       <c r="K88" s="3" t="n">
-        <v>0</v>
+        <v>2.375173</v>
       </c>
       <c r="L88" s="3" t="n">
-        <v>0</v>
+        <v>2.375173</v>
       </c>
       <c r="M88" s="3" t="n">
-        <v>0</v>
+        <v>2.375173</v>
       </c>
       <c r="N88" s="3" t="n">
-        <v>0</v>
+        <v>2.625173</v>
       </c>
     </row>
     <row r="89">
@@ -7259,7 +7259,11 @@
           <t>Share capital – Note 6</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>-</t>
@@ -7737,7 +7741,11 @@
           <t>Share capital – Note 5</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>-</t>
@@ -8584,7 +8592,11 @@
           <t>Share capital – Note 5</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
           <t>-</t>
@@ -9536,7 +9548,11 @@
           <t>Share capital – Note 5</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
           <t>-</t>
@@ -10680,7 +10696,11 @@
           <t>Share capital – Note 6</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr"/>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E49" s="5" t="n">
         <v>0.988117</v>
       </c>
@@ -20235,7 +20255,11 @@
           <t>Depletion, depreciation and amortization – Note 4</t>
         </is>
       </c>
-      <c r="D170" t="inlineStr"/>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>DepreciationAndAmortization</t>
+        </is>
+      </c>
       <c r="E170" t="inlineStr">
         <is>
           <t>-</t>
@@ -21355,7 +21379,11 @@
           <t>Depletion, depreciation and amortization – Note 5</t>
         </is>
       </c>
-      <c r="D184" t="inlineStr"/>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>DepreciationAndAmortization</t>
+        </is>
+      </c>
       <c r="E184" s="5" t="n">
         <v>0.011138</v>
       </c>

--- a/output/pdf_financials_xlsx/CHY.H.xlsx
+++ b/output/pdf_financials_xlsx/CHY.H.xlsx
@@ -13350,7 +13350,11 @@
           <t>Proceeds from private placement</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr"/>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E83" t="inlineStr">
         <is>
           <t>-</t>
